--- a/Output/ModelAggregates/SecondaryModels.xlsx
+++ b/Output/ModelAggregates/SecondaryModels.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -412,15 +412,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>p.adjust_Bonferroni.x</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>p.adjust_Bonferroni.y</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>p_adjust_fdr_full</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>p.adjust_Bonferroni</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>p_adjust_fdr_interaction</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>p_adjust_fdr</t>
         </is>
@@ -597,12 +612,12 @@
       <c r="K5" t="b">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>0.364</v>
-      </c>
       <c r="N5">
         <v>0.364</v>
       </c>
+      <c r="Q5">
+        <v>0.364</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -904,12 +919,6 @@
       <c r="K12" t="b">
         <v>1</v>
       </c>
-      <c r="M12">
-        <v>0.945</v>
-      </c>
-      <c r="N12">
-        <v>0.945</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1082,12 +1091,12 @@
       <c r="K16" t="b">
         <v>1</v>
       </c>
-      <c r="L16">
-        <v>0.364</v>
-      </c>
       <c r="N16">
         <v>0.364</v>
       </c>
+      <c r="Q16">
+        <v>0.364</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1389,12 +1398,6 @@
       <c r="K23" t="b">
         <v>1</v>
       </c>
-      <c r="M23">
-        <v>0.245</v>
-      </c>
-      <c r="N23">
-        <v>0.245</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1567,12 +1570,12 @@
       <c r="K27" t="b">
         <v>1</v>
       </c>
-      <c r="L27">
-        <v>0.889</v>
-      </c>
       <c r="N27">
         <v>0.889</v>
       </c>
+      <c r="Q27">
+        <v>0.889</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1874,11 +1877,741 @@
       <c r="K34" t="b">
         <v>1</v>
       </c>
-      <c r="M34">
-        <v>0.945</v>
-      </c>
-      <c r="N34">
-        <v>0.945</v>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FSS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>(Intercept)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>4.688</v>
+      </c>
+      <c r="E35">
+        <v>0.307</v>
+      </c>
+      <c r="F35">
+        <v>49.429</v>
+      </c>
+      <c r="G35">
+        <v>3.978</v>
+      </c>
+      <c r="H35">
+        <v>5.397</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FSS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>timepointfollowup</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>-0.029</v>
+      </c>
+      <c r="E36">
+        <v>0.309</v>
+      </c>
+      <c r="F36">
+        <v>45.415</v>
+      </c>
+      <c r="G36">
+        <v>-0.745</v>
+      </c>
+      <c r="H36">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="I36">
+        <v>0.926</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FSS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sexM</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>-0.227</v>
+      </c>
+      <c r="E37">
+        <v>0.53</v>
+      </c>
+      <c r="F37">
+        <v>48.012</v>
+      </c>
+      <c r="G37">
+        <v>-1.453</v>
+      </c>
+      <c r="H37">
+        <v>0.999</v>
+      </c>
+      <c r="I37">
+        <v>0.67</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FSS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ifn_1_netto</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>0.06</v>
+      </c>
+      <c r="E38">
+        <v>0.092</v>
+      </c>
+      <c r="F38">
+        <v>49.114</v>
+      </c>
+      <c r="G38">
+        <v>-0.152</v>
+      </c>
+      <c r="H38">
+        <v>0.272</v>
+      </c>
+      <c r="I38">
+        <v>0.516</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FSS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>timepointfollowup:treatexercise</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>-0.66</v>
+      </c>
+      <c r="E39">
+        <v>0.394</v>
+      </c>
+      <c r="F39">
+        <v>43.974</v>
+      </c>
+      <c r="G39">
+        <v>-1.575</v>
+      </c>
+      <c r="H39">
+        <v>0.256</v>
+      </c>
+      <c r="I39">
+        <v>0.101</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0.203</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FSS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>timepointfollowup:ifn_1_netto</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>-0.005</v>
+      </c>
+      <c r="E40">
+        <v>0.089</v>
+      </c>
+      <c r="F40">
+        <v>45.457</v>
+      </c>
+      <c r="G40">
+        <v>-0.21</v>
+      </c>
+      <c r="H40">
+        <v>0.2</v>
+      </c>
+      <c r="I40">
+        <v>0.957</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FSS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>timepointfollowup:treatexercise:ifn_1_netto</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>0.294</v>
+      </c>
+      <c r="E41">
+        <v>0.125</v>
+      </c>
+      <c r="F41">
+        <v>43.968</v>
+      </c>
+      <c r="G41">
+        <v>0.004</v>
+      </c>
+      <c r="H41">
+        <v>0.584</v>
+      </c>
+      <c r="I41">
+        <v>0.023</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>0.047</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>(Intercept)</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>29.929</v>
+      </c>
+      <c r="E42">
+        <v>1.61</v>
+      </c>
+      <c r="F42">
+        <v>50.096</v>
+      </c>
+      <c r="G42">
+        <v>26.695</v>
+      </c>
+      <c r="H42">
+        <v>33.162</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>timepointbaseline</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>-1.404</v>
+      </c>
+      <c r="E43">
+        <v>0.678</v>
+      </c>
+      <c r="F43">
+        <v>47.054</v>
+      </c>
+      <c r="G43">
+        <v>-2.767</v>
+      </c>
+      <c r="H43">
+        <v>-0.04</v>
+      </c>
+      <c r="I43">
+        <v>0.044</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0.08799999999999999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>timepointfollowup</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>-1.132</v>
+      </c>
+      <c r="E44">
+        <v>0.982</v>
+      </c>
+      <c r="F44">
+        <v>46.672</v>
+      </c>
+      <c r="G44">
+        <v>-3.107</v>
+      </c>
+      <c r="H44">
+        <v>0.844</v>
+      </c>
+      <c r="I44">
+        <v>0.255</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sexM</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>3.65</v>
+      </c>
+      <c r="E45">
+        <v>2.512</v>
+      </c>
+      <c r="F45">
+        <v>49.274</v>
+      </c>
+      <c r="G45">
+        <v>-1.397</v>
+      </c>
+      <c r="H45">
+        <v>8.696</v>
+      </c>
+      <c r="I45">
+        <v>0.153</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0.305</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ifn_1_netto</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>-0.753</v>
+      </c>
+      <c r="E46">
+        <v>0.485</v>
+      </c>
+      <c r="F46">
+        <v>49.263</v>
+      </c>
+      <c r="G46">
+        <v>-1.727</v>
+      </c>
+      <c r="H46">
+        <v>0.221</v>
+      </c>
+      <c r="I46">
+        <v>0.127</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>timepointfollowup:treatexercise</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>3.325</v>
+      </c>
+      <c r="E47">
+        <v>1.209</v>
+      </c>
+      <c r="F47">
+        <v>41.768</v>
+      </c>
+      <c r="G47">
+        <v>0.885</v>
+      </c>
+      <c r="H47">
+        <v>5.766</v>
+      </c>
+      <c r="I47">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>timepointbaseline:ifn_1_netto</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="E48">
+        <v>0.211</v>
+      </c>
+      <c r="F48">
+        <v>47.341</v>
+      </c>
+      <c r="G48">
+        <v>-0.513</v>
+      </c>
+      <c r="H48">
+        <v>0.337</v>
+      </c>
+      <c r="I48">
+        <v>0.679</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>timepointfollowup:ifn_1_netto</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>0.105</v>
+      </c>
+      <c r="E49">
+        <v>0.29</v>
+      </c>
+      <c r="F49">
+        <v>46.146</v>
+      </c>
+      <c r="G49">
+        <v>-0.478</v>
+      </c>
+      <c r="H49">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I49">
+        <v>0.718</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aerobic Capacity (ml/kg/min)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>timepointfollowup:treatexercise:ifn_1_netto</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>-0.554</v>
+      </c>
+      <c r="E50">
+        <v>0.403</v>
+      </c>
+      <c r="F50">
+        <v>40.761</v>
+      </c>
+      <c r="G50">
+        <v>-1.368</v>
+      </c>
+      <c r="H50">
+        <v>0.261</v>
+      </c>
+      <c r="I50">
+        <v>0.177</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Interaction effects</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <v>0.354</v>
       </c>
     </row>
   </sheetData>
